--- a/results/section3.xlsx
+++ b/results/section3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -375,10 +375,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -387,60 +387,54 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2">
         <v>100</v>
       </c>
-      <c r="C2">
+      <c r="F2">
         <v>200</v>
       </c>
-      <c r="D2">
-        <v>300</v>
-      </c>
-      <c r="E2">
-        <v>400</v>
-      </c>
-      <c r="F2">
+      <c r="G2">
         <v>500</v>
       </c>
-      <c r="G2">
-        <v>600</v>
-      </c>
       <c r="H2">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="I2">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="J2">
-        <v>900</v>
+        <v>5000</v>
       </c>
       <c r="K2">
-        <v>1000</v>
-      </c>
-      <c r="L2">
-        <v>5000</v>
-      </c>
-      <c r="M2">
         <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -456,7 +450,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -465,7 +459,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section3.xlsx
+++ b/results/section3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,16 +21,16 @@
     <t>Desis</t>
   </si>
   <si>
-    <t>Disco</t>
-  </si>
-  <si>
-    <t>Scotty</t>
-  </si>
-  <si>
     <t>DesisCen</t>
   </si>
   <si>
     <t>Real Data</t>
+  </si>
+  <si>
+    <t>DesisSW</t>
+  </si>
+  <si>
+    <t>DesisIC</t>
   </si>
 </sst>
 </file>
@@ -46,15 +46,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,15 +68,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -375,68 +398,174 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2">
+        <v>100</v>
+      </c>
+      <c r="E2" s="2">
+        <v>200</v>
+      </c>
+      <c r="F2" s="2">
+        <v>500</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H2" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I2" s="2">
+        <v>5000</v>
+      </c>
+      <c r="J2" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>25037257.879452299</v>
+      </c>
+      <c r="C3" s="3">
+        <v>24390015.5571982</v>
+      </c>
+      <c r="D3" s="3">
+        <v>24248868.7782805</v>
+      </c>
+      <c r="E3" s="3">
+        <v>24602546.021377601</v>
+      </c>
+      <c r="F3" s="3">
+        <v>23256023.719046202</v>
+      </c>
+      <c r="G3" s="3">
+        <v>23686170.698886599</v>
+      </c>
+      <c r="H3" s="3">
+        <v>23284746.213538699</v>
+      </c>
+      <c r="I3" s="3">
+        <v>23700784.040825699</v>
+      </c>
+      <c r="J3" s="3">
+        <v>23483457.718751799</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>7087908.7199999997</v>
+      </c>
+      <c r="C4" s="3">
+        <v>7115832.4800000004</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7088310.5199999996</v>
+      </c>
+      <c r="E4" s="3">
+        <v>7082815.0099999998</v>
+      </c>
+      <c r="F4" s="3">
+        <v>6926315.1699999999</v>
+      </c>
+      <c r="G4" s="3">
+        <v>7110177.0659999996</v>
+      </c>
+      <c r="H4" s="3">
+        <v>6842615.5800000001</v>
+      </c>
+      <c r="I4" s="3">
+        <v>6916566.4000000004</v>
+      </c>
+      <c r="J4" s="3">
+        <v>7062998.5300000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>3769428.71</v>
+      </c>
+      <c r="C5" s="3">
+        <v>614002.09</v>
+      </c>
+      <c r="D5" s="3">
+        <v>276933.59000000003</v>
+      </c>
+      <c r="E5" s="3">
+        <v>113125.26</v>
+      </c>
+      <c r="F5" s="3">
+        <v>50027.37</v>
+      </c>
+      <c r="G5" s="3">
+        <v>25677.109</v>
+      </c>
+      <c r="H5" s="3">
+        <v>8050.6480000000001</v>
+      </c>
+      <c r="I5" s="3">
+        <v>4493.9579999999996</v>
+      </c>
+      <c r="J5" s="3">
+        <v>3556.81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>50</v>
-      </c>
-      <c r="E2">
-        <v>100</v>
-      </c>
-      <c r="F2">
-        <v>200</v>
-      </c>
-      <c r="G2">
-        <v>500</v>
-      </c>
-      <c r="H2">
-        <v>1000</v>
-      </c>
-      <c r="I2">
-        <v>2000</v>
-      </c>
-      <c r="J2">
-        <v>5000</v>
-      </c>
-      <c r="K2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
+      <c r="B6" s="3">
+        <v>80904.27</v>
+      </c>
+      <c r="C6" s="3">
+        <v>77070.0052</v>
+      </c>
+      <c r="D6" s="3">
+        <v>100287.23</v>
+      </c>
+      <c r="E6" s="3">
+        <v>85969.64</v>
+      </c>
+      <c r="F6" s="3">
+        <v>45931.539900000003</v>
+      </c>
+      <c r="G6" s="3">
+        <v>5836.9430000000002</v>
+      </c>
+      <c r="H6" s="3">
+        <v>569.05557999999996</v>
+      </c>
+      <c r="I6" s="3">
+        <v>3317.3285999999998</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1436.5351599999999</v>
       </c>
     </row>
   </sheetData>
@@ -450,7 +579,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -459,7 +588,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section3.xlsx
+++ b/results/section3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89,11 +89,11 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,49 +399,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1">
         <v>10</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>50</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>100</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>200</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>500</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>1000</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>2000</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="1">
         <v>5000</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3">
@@ -472,8 +479,8 @@
         <v>23483457.718751799</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="3">
@@ -504,8 +511,8 @@
         <v>7062998.5300000003</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3">
@@ -536,8 +543,8 @@
         <v>3556.81</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="3">
@@ -573,13 +580,14 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -588,7 +596,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section3.xlsx
+++ b/results/section3.xlsx
@@ -87,13 +87,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -408,16 +409,16 @@
     <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1">
         <v>10</v>
@@ -446,134 +447,182 @@
       <c r="J2" s="1">
         <v>10000</v>
       </c>
+      <c r="K2" s="1">
+        <v>50000</v>
+      </c>
+      <c r="L2" s="1">
+        <v>100000</v>
+      </c>
+      <c r="M2" s="1">
+        <v>500000</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1000000</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>25037257.879452299</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>24390015.5571982</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>24248868.7782805</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>24602546.021377601</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>23256023.719046202</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>23686170.698886599</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>23284746.213538699</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <v>23700784.040825699</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>23483457.718751799</v>
       </c>
+      <c r="K3" s="4">
+        <v>24658974.783178601</v>
+      </c>
+      <c r="L3" s="4">
+        <v>19009147.372923002</v>
+      </c>
+      <c r="M3" s="4">
+        <v>17712309.547367699</v>
+      </c>
+      <c r="N3" s="1">
+        <v>3181.5318439522198</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>7087908.7199999997</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>7115832.4800000004</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>7088310.5199999996</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>7082815.0099999998</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>6926315.1699999999</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>7110177.0659999996</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>6842615.5800000001</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <v>6916566.4000000004</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>7062998.5300000003</v>
       </c>
+      <c r="K4" s="1">
+        <v>6664863.7980000004</v>
+      </c>
+      <c r="L4" s="1">
+        <v>5831647.5800000001</v>
+      </c>
+      <c r="M4" s="1">
+        <v>5085647.68</v>
+      </c>
+      <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>3769428.71</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>614002.09</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>276933.59000000003</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>113125.26</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>50027.37</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>25677.109</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>8050.6480000000001</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>4493.9579999999996</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>3556.81</v>
       </c>
+      <c r="K5" s="1">
+        <v>3232.43</v>
+      </c>
+      <c r="L5" s="1">
+        <v>3217.23</v>
+      </c>
+      <c r="M5" s="1">
+        <v>3189.73</v>
+      </c>
+      <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>80904.27</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>77070.0052</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>100287.23</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>85969.64</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>45931.539900000003</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>5836.9430000000002</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <v>569.05557999999996</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <v>3317.3285999999998</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <v>1436.5351599999999</v>
       </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/results/section3.xlsx
+++ b/results/section3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,16 +400,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -418,49 +419,49 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>10</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>50</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>100</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>200</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>500</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <v>1000</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="2">
         <v>2000</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="2">
         <v>5000</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <v>10000</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="2">
         <v>50000</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="2">
         <v>100000</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="2">
         <v>500000</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="2">
         <v>1000000</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -491,20 +492,20 @@
       <c r="J3" s="2">
         <v>23483457.718751799</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="2">
         <v>24658974.783178601</v>
       </c>
       <c r="L3" s="4">
+        <v>21502353.915197901</v>
+      </c>
+      <c r="M3" s="2">
         <v>19009147.372923002</v>
       </c>
-      <c r="M3" s="4">
+      <c r="N3" s="2">
         <v>17712309.547367699</v>
       </c>
-      <c r="N3" s="1">
-        <v>3181.5318439522198</v>
-      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -535,18 +536,20 @@
       <c r="J4" s="2">
         <v>7062998.5300000003</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="2">
         <v>6664863.7980000004</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4" s="2">
         <v>5831647.5800000001</v>
       </c>
-      <c r="M4" s="1">
+      <c r="M4" s="2">
         <v>5085647.68</v>
       </c>
-      <c r="N4" s="1"/>
+      <c r="N4" s="4">
+        <v>4604147.1950000003</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -577,18 +580,20 @@
       <c r="J5" s="2">
         <v>3556.81</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5" s="2">
         <v>3232.43</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5" s="2">
         <v>3217.23</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5" s="2">
         <v>3189.73</v>
       </c>
-      <c r="N5" s="1"/>
+      <c r="N5" s="2">
+        <v>3060.95</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -617,12 +622,20 @@
         <v>3317.3285999999998</v>
       </c>
       <c r="J6" s="2">
-        <v>1436.5351599999999</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
+        <v>3239.6323659999998</v>
+      </c>
+      <c r="K6" s="2">
+        <v>3187.9418999999998</v>
+      </c>
+      <c r="L6" s="2">
+        <v>3157.7109999999998</v>
+      </c>
+      <c r="M6" s="2">
+        <v>3118.2858999999999</v>
+      </c>
+      <c r="N6" s="2">
+        <v>3089.3564999999999</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -636,7 +649,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -645,7 +658,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section3.xlsx
+++ b/results/section3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>Desis</t>
   </si>
@@ -91,10 +91,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,27 +399,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.90625" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="2">
         <v>10</v>
@@ -461,51 +461,51 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>25037257.879452299</v>
+        <v>31046199.771200001</v>
       </c>
       <c r="C3" s="2">
-        <v>24390015.5571982</v>
+        <v>30243619.294399999</v>
       </c>
       <c r="D3" s="2">
-        <v>24248868.7782805</v>
+        <v>30068597.2872</v>
       </c>
       <c r="E3" s="2">
-        <v>24602546.021377601</v>
+        <v>30507157.064800002</v>
       </c>
       <c r="F3" s="2">
-        <v>23256023.719046202</v>
+        <v>28837469.412799999</v>
       </c>
       <c r="G3" s="2">
-        <v>23686170.698886599</v>
+        <v>29370851.668000001</v>
       </c>
       <c r="H3" s="2">
-        <v>23284746.213538699</v>
+        <v>28873085.3004</v>
       </c>
       <c r="I3" s="2">
-        <v>23700784.040825699</v>
+        <v>29388972.209600002</v>
       </c>
       <c r="J3" s="2">
-        <v>23483457.718751799</v>
+        <v>29119487.572799999</v>
       </c>
       <c r="K3" s="2">
-        <v>24658974.783178601</v>
-      </c>
-      <c r="L3" s="4">
-        <v>21502353.915197901</v>
+        <v>29577128.727200001</v>
+      </c>
+      <c r="L3" s="3">
+        <v>26662918.860800002</v>
       </c>
       <c r="M3" s="2">
-        <v>19009147.372923002</v>
+        <v>23571342.7388</v>
       </c>
       <c r="N3" s="2">
-        <v>17712309.547367699</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>21963263.842</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -545,11 +545,11 @@
       <c r="M4" s="2">
         <v>5085647.68</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="3">
         <v>4604147.1950000003</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -593,7 +593,7 @@
         <v>3060.95</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -637,9 +637,237 @@
         <v>3089.3564999999999</v>
       </c>
     </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2">
+        <v>50</v>
+      </c>
+      <c r="D14" s="2">
+        <v>100</v>
+      </c>
+      <c r="E14" s="2">
+        <v>200</v>
+      </c>
+      <c r="F14" s="2">
+        <v>500</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H14" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I14" s="2">
+        <v>5000</v>
+      </c>
+      <c r="J14" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K14" s="2">
+        <v>50000</v>
+      </c>
+      <c r="L14" s="2">
+        <v>100000</v>
+      </c>
+      <c r="M14" s="2">
+        <v>500000</v>
+      </c>
+      <c r="N14" s="2">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2">
+        <v>25037257.879452299</v>
+      </c>
+      <c r="C15" s="2">
+        <v>24390015.5571982</v>
+      </c>
+      <c r="D15" s="2">
+        <v>24248868.7782805</v>
+      </c>
+      <c r="E15" s="2">
+        <v>24602546.021377601</v>
+      </c>
+      <c r="F15" s="2">
+        <v>23256023.719046202</v>
+      </c>
+      <c r="G15" s="2">
+        <v>23686170.698886599</v>
+      </c>
+      <c r="H15" s="2">
+        <v>23284746.213538699</v>
+      </c>
+      <c r="I15" s="2">
+        <v>23700784.040825699</v>
+      </c>
+      <c r="J15" s="2">
+        <v>23483457.718751799</v>
+      </c>
+      <c r="K15" s="2">
+        <v>24658974.783178601</v>
+      </c>
+      <c r="L15" s="3">
+        <v>21502353.915197901</v>
+      </c>
+      <c r="M15" s="2">
+        <v>19009147.372923002</v>
+      </c>
+      <c r="N15" s="2">
+        <v>17712309.547367699</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="2">
+        <v>7087908.7199999997</v>
+      </c>
+      <c r="C16" s="2">
+        <v>7115832.4800000004</v>
+      </c>
+      <c r="D16" s="2">
+        <v>7088310.5199999996</v>
+      </c>
+      <c r="E16" s="2">
+        <v>7082815.0099999998</v>
+      </c>
+      <c r="F16" s="2">
+        <v>6926315.1699999999</v>
+      </c>
+      <c r="G16" s="2">
+        <v>7110177.0659999996</v>
+      </c>
+      <c r="H16" s="2">
+        <v>6842615.5800000001</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6916566.4000000004</v>
+      </c>
+      <c r="J16" s="2">
+        <v>7062998.5300000003</v>
+      </c>
+      <c r="K16" s="2">
+        <v>6664863.7980000004</v>
+      </c>
+      <c r="L16" s="2">
+        <v>5831647.5800000001</v>
+      </c>
+      <c r="M16" s="2">
+        <v>5085647.68</v>
+      </c>
+      <c r="N16" s="3">
+        <v>4604147.1950000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2">
+        <v>3769428.71</v>
+      </c>
+      <c r="C17" s="2">
+        <v>614002.09</v>
+      </c>
+      <c r="D17" s="2">
+        <v>276933.59000000003</v>
+      </c>
+      <c r="E17" s="2">
+        <v>113125.26</v>
+      </c>
+      <c r="F17" s="2">
+        <v>50027.37</v>
+      </c>
+      <c r="G17" s="2">
+        <v>25677.109</v>
+      </c>
+      <c r="H17" s="2">
+        <v>8050.6480000000001</v>
+      </c>
+      <c r="I17" s="2">
+        <v>4493.9579999999996</v>
+      </c>
+      <c r="J17" s="2">
+        <v>3556.81</v>
+      </c>
+      <c r="K17" s="2">
+        <v>3232.43</v>
+      </c>
+      <c r="L17" s="2">
+        <v>3217.23</v>
+      </c>
+      <c r="M17" s="2">
+        <v>3189.73</v>
+      </c>
+      <c r="N17" s="2">
+        <v>3060.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2">
+        <v>80904.27</v>
+      </c>
+      <c r="C18" s="2">
+        <v>77070.0052</v>
+      </c>
+      <c r="D18" s="2">
+        <v>100287.23</v>
+      </c>
+      <c r="E18" s="2">
+        <v>85969.64</v>
+      </c>
+      <c r="F18" s="2">
+        <v>45931.539900000003</v>
+      </c>
+      <c r="G18" s="2">
+        <v>5836.9430000000002</v>
+      </c>
+      <c r="H18" s="2">
+        <v>569.05557999999996</v>
+      </c>
+      <c r="I18" s="2">
+        <v>3317.3285999999998</v>
+      </c>
+      <c r="J18" s="2">
+        <v>3239.6323659999998</v>
+      </c>
+      <c r="K18" s="2">
+        <v>3187.9418999999998</v>
+      </c>
+      <c r="L18" s="2">
+        <v>3157.7109999999998</v>
+      </c>
+      <c r="M18" s="2">
+        <v>3118.2858999999999</v>
+      </c>
+      <c r="N18" s="2">
+        <v>3089.3564999999999</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -649,7 +877,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -658,7 +886,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
